--- a/workbook/sentence-edits.xlsx
+++ b/workbook/sentence-edits.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,6 +505,36 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-09-29 05:38:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>97a74a40d43b</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>split</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>P4-2 UI 冒煙</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-29 06:21:57</t>
         </is>
       </c>
     </row>

--- a/workbook/sentence-edits.xlsx
+++ b/workbook/sentence-edits.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,6 +535,66 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-09-29 06:21:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4e5731ad2386</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>split</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>P4 自檢</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-30 00:19:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4e5731ad2386</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>split</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>P4 自檢</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-30 00:22:34</t>
         </is>
       </c>
     </row>

--- a/workbook/sentence-edits.xlsx
+++ b/workbook/sentence-edits.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -598,6 +598,66 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4e5731ad2386</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>split</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>P4 自檢</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:35:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>4e5731ad2386</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>split</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>P4 自檢</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:38:46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/workbook/sentence-edits.xlsx
+++ b/workbook/sentence-edits.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -658,6 +658,36 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>4e5731ad2386</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>split</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>P4 自檢</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-30 23:20:32</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/workbook/sentence-edits.xlsx
+++ b/workbook/sentence-edits.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,246 +445,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>录入时间(createdAt)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>97a74a40d43b</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>split</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>P4 测试，验完撤销</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-09-29 05:33:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>4e5731ad2386</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>split</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>P4 自檢</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-09-29 05:38:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>97a74a40d43b</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>split</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>P4-2 UI 冒煙</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-09-29 06:21:57</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4e5731ad2386</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>split</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>P4 自檢</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-09-30 00:19:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>4e5731ad2386</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>split</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>P4 自檢</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-09-30 00:22:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>4e5731ad2386</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>split</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>P4 自檢</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-09-30 06:35:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>4e5731ad2386</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>split</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>P4 自檢</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-09-30 06:38:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>4e5731ad2386</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>split</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>P4 自檢</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-09-30 23:20:32</t>
         </is>
       </c>
     </row>
